--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555799909</v>
+        <v>46157.93113759853</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113759853</v>
+        <v>46157.93137207461</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137207461</v>
+        <v>46157.93384703764</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384703764</v>
+        <v>46157.93696402073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696402073</v>
+        <v>46158.28205292847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205292847</v>
+        <v>46158.29653230809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653230809</v>
+        <v>46158.29808255854</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808255854</v>
+        <v>46158.33371085973</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371085973</v>
+        <v>46158.3722240097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Октябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3722240097</v>
+        <v>46158.37275962468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
